--- a/META.xlsx
+++ b/META.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\CCTRL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21989ACB-1323-45FB-B557-2257FA9E82E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8429D07C-5937-454A-A0D7-358B4307A21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7E2EB6A9-E1E3-47B2-841B-3B5C1A483F44}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>META</t>
   </si>
@@ -123,8 +123,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}" name="Tabla1" displayName="Tabla1" ref="B2:D7" totalsRowShown="0">
-  <autoFilter ref="B2:D7" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}" name="Tabla1" displayName="Tabla1" ref="B2:D12" totalsRowShown="0">
+  <autoFilter ref="B2:D12" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{EB4DC0C5-072B-4CD3-866A-34D4637439F5}" name="COTRATISTA"/>
     <tableColumn id="2" xr3:uid="{2B71B625-C631-4A97-A6AB-5BA61233941F}" name="META"/>
@@ -451,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F920B9B8-A44E-4F3A-B014-1F6EDBC2A6C5}">
-  <dimension ref="B2:D7"/>
+  <dimension ref="B2:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -524,6 +524,61 @@
         <v>46204</v>
       </c>
     </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>10488</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>4800</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46235</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/META.xlsx
+++ b/META.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\CCTRL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8429D07C-5937-454A-A0D7-358B4307A21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471DB211-7FCA-432E-9565-9EBE817C09B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7E2EB6A9-E1E3-47B2-841B-3B5C1A483F44}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
   <si>
     <t>META</t>
   </si>
@@ -123,8 +123,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}" name="Tabla1" displayName="Tabla1" ref="B2:D12" totalsRowShown="0">
-  <autoFilter ref="B2:D12" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}" name="Tabla1" displayName="Tabla1" ref="B2:D16" totalsRowShown="0">
+  <autoFilter ref="B2:D16" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{EB4DC0C5-072B-4CD3-866A-34D4637439F5}" name="COTRATISTA"/>
     <tableColumn id="2" xr3:uid="{2B71B625-C631-4A97-A6AB-5BA61233941F}" name="META"/>
@@ -451,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F920B9B8-A44E-4F3A-B014-1F6EDBC2A6C5}">
-  <dimension ref="B2:D12"/>
+  <dimension ref="B2:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -579,6 +579,50 @@
         <v>46235</v>
       </c>
     </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>11653</v>
+      </c>
+      <c r="D13" s="1">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>20000</v>
+      </c>
+      <c r="D16" s="1">
+        <v>46266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/META.xlsx
+++ b/META.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\CCTRL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471DB211-7FCA-432E-9565-9EBE817C09B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCDC98D-7C0A-4F69-A032-758291CD3415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7E2EB6A9-E1E3-47B2-841B-3B5C1A483F44}"/>
   </bookViews>
@@ -606,7 +606,7 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="D15" s="1">
         <v>46266</v>
@@ -617,7 +617,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="D16" s="1">
         <v>46266</v>

--- a/META.xlsx
+++ b/META.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\CCTRL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCDC98D-7C0A-4F69-A032-758291CD3415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF2CC60-77C1-46E9-8044-8D237089042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7E2EB6A9-E1E3-47B2-841B-3B5C1A483F44}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="8">
   <si>
     <t>META</t>
   </si>
@@ -123,8 +123,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}" name="Tabla1" displayName="Tabla1" ref="B2:D16" totalsRowShown="0">
-  <autoFilter ref="B2:D16" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}" name="Tabla1" displayName="Tabla1" ref="B2:D20" totalsRowShown="0">
+  <autoFilter ref="B2:D20" xr:uid="{F482E87D-5CEB-4F2E-A5E3-C1C0138E0706}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{EB4DC0C5-072B-4CD3-866A-34D4637439F5}" name="COTRATISTA"/>
     <tableColumn id="2" xr3:uid="{2B71B625-C631-4A97-A6AB-5BA61233941F}" name="META"/>
@@ -451,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F920B9B8-A44E-4F3A-B014-1F6EDBC2A6C5}">
-  <dimension ref="B2:D16"/>
+  <dimension ref="B2:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -623,6 +623,50 @@
         <v>46266</v>
       </c>
     </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>11676</v>
+      </c>
+      <c r="D17" s="1">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>4200</v>
+      </c>
+      <c r="D18" s="1">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>6400</v>
+      </c>
+      <c r="D19" s="1">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>10000</v>
+      </c>
+      <c r="D20" s="1">
+        <v>46296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
